--- a/artfynd/A 49376-2023 artfynd.xlsx
+++ b/artfynd/A 49376-2023 artfynd.xlsx
@@ -803,11 +803,11 @@
         <v>119323921</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
+        <v>92251</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 49376-2023 artfynd.xlsx
+++ b/artfynd/A 49376-2023 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>119323921</v>
       </c>
       <c r="B3" t="n">
-        <v>92251</v>
+        <v>92254</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49376-2023 artfynd.xlsx
+++ b/artfynd/A 49376-2023 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>119323921</v>
       </c>
       <c r="B3" t="n">
-        <v>92254</v>
+        <v>92256</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49376-2023 artfynd.xlsx
+++ b/artfynd/A 49376-2023 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>119323921</v>
       </c>
       <c r="B3" t="n">
-        <v>92256</v>
+        <v>92262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49376-2023 artfynd.xlsx
+++ b/artfynd/A 49376-2023 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>119323921</v>
       </c>
       <c r="B3" t="n">
-        <v>92262</v>
+        <v>92265</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49376-2023 artfynd.xlsx
+++ b/artfynd/A 49376-2023 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>119323921</v>
       </c>
       <c r="B3" t="n">
-        <v>92265</v>
+        <v>92282</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49376-2023 artfynd.xlsx
+++ b/artfynd/A 49376-2023 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>119323921</v>
       </c>
       <c r="B3" t="n">
-        <v>92282</v>
+        <v>92287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 49376-2023 artfynd.xlsx
+++ b/artfynd/A 49376-2023 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>119323921</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92289</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
